--- a/lab-standards/BSIA-lab-standard.xlsx
+++ b/lab-standards/BSIA-lab-standard.xlsx
@@ -560,6 +560,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -572,6 +576,10 @@
           <t>Computer Lab (400 sft) and Workshop (700–800 sft) for 25 trainees</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -641,7 +649,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -663,7 +673,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
       </c>
@@ -685,7 +697,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -707,7 +721,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -729,7 +745,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -751,7 +769,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -773,7 +793,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -795,7 +817,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -817,7 +841,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -839,7 +865,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -861,7 +889,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -883,7 +913,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -905,7 +937,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>9</v>
       </c>
@@ -927,7 +961,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>10</v>
       </c>
@@ -949,7 +985,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>9</v>
       </c>
@@ -971,7 +1009,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -993,7 +1033,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>8</v>
       </c>
@@ -1015,7 +1057,9 @@
       <c r="C33" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>7</v>
       </c>
@@ -1037,7 +1081,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -1183,6 +1229,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1195,6 +1245,10 @@
           <t>Computer Lab (400 sft) and Workshop (700–800 sft) for 25 trainees</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1264,7 +1318,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -1286,7 +1342,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
       </c>
@@ -1308,7 +1366,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -1330,7 +1390,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1352,7 +1414,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -1374,7 +1438,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1396,7 +1462,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1418,7 +1486,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1440,7 +1510,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -1462,7 +1534,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1484,7 +1558,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>9</v>
       </c>
@@ -1506,7 +1582,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -1528,7 +1606,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>10</v>
       </c>
@@ -1550,7 +1630,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -1572,7 +1654,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -1594,7 +1678,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -1616,7 +1702,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1638,7 +1726,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1660,7 +1750,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -1806,6 +1898,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1818,6 +1914,10 @@
           <t>Computer Lab (400 sft) and Workshop (700–800 sft) for 25 trainees; stationery</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1887,7 +1987,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -1909,7 +2011,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
       </c>
@@ -1931,7 +2035,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -1953,7 +2059,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1975,7 +2083,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -1997,7 +2107,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>10</v>
       </c>
@@ -2019,7 +2131,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -2041,7 +2155,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -2063,7 +2179,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -2085,7 +2203,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -2107,7 +2227,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>9</v>
       </c>
@@ -2129,7 +2251,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -2151,7 +2275,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -2173,7 +2299,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -2195,7 +2323,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -2217,7 +2347,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -2239,7 +2371,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -2261,7 +2395,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -2283,7 +2419,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -2429,6 +2567,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2441,6 +2583,10 @@
           <t>Power electronics lab (approx. for 25 trainees) with benches, storage and stationery</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2510,7 +2656,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>6</v>
       </c>
@@ -2532,7 +2680,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -2554,7 +2704,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -2576,7 +2728,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -2598,7 +2752,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2620,7 +2776,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -2642,7 +2800,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -2664,7 +2824,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>10</v>
       </c>
@@ -2686,7 +2848,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -2708,7 +2872,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -2730,7 +2896,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>9</v>
       </c>
@@ -2752,7 +2920,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -2774,7 +2944,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -2796,7 +2968,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -2818,7 +2992,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -2840,7 +3016,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -2862,7 +3040,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -2884,7 +3064,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -2906,7 +3088,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -3052,6 +3236,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3064,6 +3252,10 @@
           <t>Embedded/electronics lab (approx. for 25 trainees) with benches, storage and stationery</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3133,7 +3325,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>6</v>
       </c>
@@ -3155,7 +3349,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -3177,7 +3373,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -3199,7 +3397,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -3221,7 +3421,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -3243,7 +3445,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -3265,7 +3469,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -3287,7 +3493,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -3309,7 +3517,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -3331,7 +3541,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -3353,7 +3565,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -3375,7 +3589,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -3397,7 +3613,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -3419,7 +3637,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -3441,7 +3661,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>9</v>
       </c>
@@ -3463,7 +3685,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -3485,7 +3709,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -3507,7 +3733,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -3529,7 +3757,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
